--- a/project-governance/master-gantt.xlsx
+++ b/project-governance/master-gantt.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simple Gantt" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current Gantt" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Simple Gantt'!$A$8:$P$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Simple Gantt'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Simple Gantt'!$A$1:$P$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Current Gantt'!$A$8:$P$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Current Gantt'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Current Gantt'!$A$1:$P$35</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -20,12 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="d mmm"/>
-    <numFmt numFmtId="166" formatCode="dd mmm"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="d mmm"/>
+    <numFmt numFmtId="165" formatCode="dd mmm"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +73,18 @@
       <color rgb="00243B53"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="00607D8B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -137,8 +146,33 @@
         <fgColor rgb="00ECEFF1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001769AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B95A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F2D46"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -173,11 +207,87 @@
         <color rgb="00D9E2EC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2EC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00F9A825"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="00F9A825"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00F9A825"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -219,10 +329,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,7 +341,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,7 +355,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -266,18 +376,98 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -365,6 +555,42 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="008A94A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="001769AA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="008B95A3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="001769AA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="008B95A3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -745,12 +971,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -774,14 +1000,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Blockmediary — Simple Gantt v3</t>
+          <t>Blockmediary — Current Gantt</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Simple weekly view | 8 June–14 August 2026 | Status date 12 August 2026 | Source: v3 plan, Kanban and RACI</t>
+          <t>Weekly view | 8 June–14 August 2026 | Status date 13 August 2026 | Current completion snapshot</t>
         </is>
       </c>
     </row>
@@ -791,82 +1017,82 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
+      <c r="B4" s="37" t="n"/>
+      <c r="C4" s="38" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="E4" s="37" t="n"/>
+      <c r="F4" s="38" t="n"/>
       <c r="G4" s="6" t="inlineStr">
         <is>
           <t>DOING</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="H4" s="37" t="n"/>
+      <c r="I4" s="38" t="n"/>
       <c r="J4" s="7" t="inlineStr">
         <is>
           <t>TO DO</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="K4" s="37" t="n"/>
+      <c r="L4" s="38" t="n"/>
       <c r="M4" s="8" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
       </c>
-      <c r="N4" s="4" t="n"/>
+      <c r="N4" s="38" t="n"/>
       <c r="O4" s="9" t="inlineStr">
         <is>
           <t>ACTIVE COMPLETE</t>
         </is>
       </c>
-      <c r="P4" s="4" t="n"/>
+      <c r="P4" s="38" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10">
-        <f>COUNTIF($F$9:$F$33,"Done")</f>
-        <v>12</v>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
+        <f>COUNTIF($F$9:$F$35,"Done")</f>
+        <v>26</v>
+      </c>
+      <c r="B5" s="37" t="n"/>
+      <c r="C5" s="38" t="n"/>
       <c r="D5" s="10">
-        <f>COUNTIF($F$9:$F$33,"Review")</f>
-        <v>5</v>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+        <f>COUNTIF($F$9:$F$35,"Review")</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="37" t="n"/>
+      <c r="F5" s="38" t="n"/>
       <c r="G5" s="10">
-        <f>COUNTIF($F$9:$F$33,"Doing")</f>
-        <v>4</v>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
+        <f>COUNTIF($F$9:$F$35,"Doing")</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="37" t="n"/>
+      <c r="I5" s="38" t="n"/>
       <c r="J5" s="10">
-        <f>COUNTIF($F$9:$F$33,"To Do")</f>
-        <v>3</v>
-      </c>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
+        <f>COUNTIF($F$9:$F$35,"To Do")</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="37" t="n"/>
+      <c r="L5" s="38" t="n"/>
       <c r="M5" s="10">
-        <f>COUNTIF($F$9:$F$33,"Deferred")</f>
+        <f>COUNTIF($F$9:$F$35,"Deferred")</f>
         <v>1</v>
       </c>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="38" t="n"/>
       <c r="O5" s="11">
-        <f>COUNTIF($F$9:$F$33,"Done")/COUNTIF($F$9:$F$33,"&lt;&gt;Deferred")</f>
-        <v>0.5</v>
-      </c>
-      <c r="P5" s="4" t="n"/>
+        <f>COUNTIF($F$9:$F$35,"Done")/COUNTIF($F$9:$F$35,"&lt;&gt;Deferred")</f>
+        <v>1</v>
+      </c>
+      <c r="P5" s="38" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>July strategy tasks use a full-month bar because only July timing was supplied; exact days are not asserted.  ◆ Proposal: 8 Jun   ◆ Submission: 14 Aug</t>
+          <t>Bars show the planned schedule.  ◆ Proposal: 8 Jun   ◆ Status: 13 Aug   ◆ Submission: 14 Aug</t>
         </is>
       </c>
     </row>
@@ -918,985 +1144,1061 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="59" t="n">
         <v>46181</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="59" t="n">
         <v>46188</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="59" t="n">
         <v>46195</v>
       </c>
-      <c r="J8" s="16" t="n">
+      <c r="J8" s="59" t="n">
         <v>46202</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="59" t="n">
         <v>46209</v>
       </c>
-      <c r="L8" s="16" t="n">
+      <c r="L8" s="59" t="n">
         <v>46216</v>
       </c>
-      <c r="M8" s="16" t="n">
+      <c r="M8" s="59" t="n">
         <v>46223</v>
       </c>
-      <c r="N8" s="16" t="n">
+      <c r="N8" s="60" t="n">
         <v>46230</v>
       </c>
-      <c r="O8" s="16" t="n">
+      <c r="O8" s="59" t="n">
         <v>46237</v>
       </c>
-      <c r="P8" s="15" t="n">
+      <c r="P8" s="61" t="n">
         <v>46244</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>GOV-01</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>Proposal handoff</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>Tamer (A/R)</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="44" t="n">
         <v>46181</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="44" t="n">
         <v>46181</v>
       </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="22" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="22" t="n"/>
-      <c r="N9" s="22" t="n"/>
-      <c r="O9" s="22" t="n"/>
-      <c r="P9" s="22" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="F9" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="47" t="n"/>
+      <c r="I9" s="47" t="n"/>
+      <c r="J9" s="47" t="n"/>
+      <c r="K9" s="47" t="n"/>
+      <c r="L9" s="47" t="n"/>
+      <c r="M9" s="47" t="n"/>
+      <c r="N9" s="47" t="n"/>
+      <c r="O9" s="47" t="n"/>
+      <c r="P9" s="62" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="48" t="inlineStr">
         <is>
           <t>GOV-02</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>Requirements and governance baseline</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>Tamer (A); Nick and Dan (R)</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="50" t="n">
         <v>46182</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="50" t="n">
         <v>46194</v>
       </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="F10" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G10" s="46" t="n"/>
+      <c r="H10" s="46" t="n"/>
+      <c r="I10" s="47" t="n"/>
+      <c r="J10" s="47" t="n"/>
+      <c r="K10" s="47" t="n"/>
+      <c r="L10" s="47" t="n"/>
+      <c r="M10" s="47" t="n"/>
+      <c r="N10" s="47" t="n"/>
+      <c r="O10" s="47" t="n"/>
+      <c r="P10" s="62" t="n"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>GOV-03</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>Project coordination through submission</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>Tamer (A/R); Dan (R)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="44" t="n">
         <v>46182</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="44" t="n">
         <v>46248</v>
       </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>Doing</t>
-        </is>
-      </c>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-      <c r="O11" s="27" t="n"/>
-      <c r="P11" s="27" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="F11" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G11" s="46" t="n"/>
+      <c r="H11" s="46" t="n"/>
+      <c r="I11" s="46" t="n"/>
+      <c r="J11" s="46" t="n"/>
+      <c r="K11" s="46" t="n"/>
+      <c r="L11" s="46" t="n"/>
+      <c r="M11" s="46" t="n"/>
+      <c r="N11" s="46" t="n"/>
+      <c r="O11" s="46" t="n"/>
+      <c r="P11" s="63" t="n"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>STR-01</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>Market research</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>Tamer (A/R); Conrad and Mo (C)</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="50" t="n">
         <v>46204</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="50" t="n">
+        <v>46210</v>
+      </c>
+      <c r="F12" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" s="47" t="n"/>
+      <c r="H12" s="47" t="n"/>
+      <c r="I12" s="47" t="n"/>
+      <c r="J12" s="46" t="n"/>
+      <c r="K12" s="46" t="n"/>
+      <c r="L12" s="47" t="n"/>
+      <c r="M12" s="47" t="n"/>
+      <c r="N12" s="47" t="n"/>
+      <c r="O12" s="47" t="n"/>
+      <c r="P12" s="62" t="n"/>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>STR-02</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Strategic analysis</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>Tamer (A/R); all leads (C)</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E13" s="44" t="n">
+        <v>46217</v>
+      </c>
+      <c r="F13" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" s="47" t="n"/>
+      <c r="H13" s="47" t="n"/>
+      <c r="I13" s="47" t="n"/>
+      <c r="J13" s="47" t="n"/>
+      <c r="K13" s="46" t="n"/>
+      <c r="L13" s="46" t="n"/>
+      <c r="M13" s="47" t="n"/>
+      <c r="N13" s="47" t="n"/>
+      <c r="O13" s="47" t="n"/>
+      <c r="P13" s="62" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="48" t="inlineStr">
+        <is>
+          <t>STR-03</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Strategic planning</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>Tamer (A/R); all leads (C)</t>
+        </is>
+      </c>
+      <c r="D14" s="50" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E14" s="50" t="n">
+        <v>46224</v>
+      </c>
+      <c r="F14" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G14" s="47" t="n"/>
+      <c r="H14" s="47" t="n"/>
+      <c r="I14" s="47" t="n"/>
+      <c r="J14" s="47" t="n"/>
+      <c r="K14" s="47" t="n"/>
+      <c r="L14" s="46" t="n"/>
+      <c r="M14" s="46" t="n"/>
+      <c r="N14" s="47" t="n"/>
+      <c r="O14" s="47" t="n"/>
+      <c r="P14" s="62" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>STR-04</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Financial and legal coordination and oversight</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>Tamer (A/R); Conrad and Badhri (C)</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E15" s="44" t="n">
         <v>46234</v>
       </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="22" t="n"/>
-      <c r="P12" s="22" t="n"/>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>STR-02</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>Strategic analysis</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>Tamer (A/R); all leads (C)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="22" t="n"/>
-      <c r="P13" s="22" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>STR-03</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Strategic planning</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>Tamer (A/R); all leads (C)</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="22" t="n"/>
-      <c r="P14" s="22" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>STR-04</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Financial and legal coordination and oversight</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="F15" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G15" s="47" t="n"/>
+      <c r="H15" s="47" t="n"/>
+      <c r="I15" s="47" t="n"/>
+      <c r="J15" s="46" t="n"/>
+      <c r="K15" s="46" t="n"/>
+      <c r="L15" s="46" t="n"/>
+      <c r="M15" s="46" t="n"/>
+      <c r="N15" s="46" t="n"/>
+      <c r="O15" s="47" t="n"/>
+      <c r="P15" s="62" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>PRD-01</t>
+        </is>
+      </c>
+      <c r="B16" s="49" t="inlineStr">
+        <is>
+          <t>Product workflow and release rules</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="inlineStr">
+        <is>
+          <t>Dan (A/R); Nick (R)</t>
+        </is>
+      </c>
+      <c r="D16" s="50" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" s="46" t="n"/>
+      <c r="H16" s="46" t="n"/>
+      <c r="I16" s="46" t="n"/>
+      <c r="J16" s="46" t="n"/>
+      <c r="K16" s="46" t="n"/>
+      <c r="L16" s="47" t="n"/>
+      <c r="M16" s="47" t="n"/>
+      <c r="N16" s="47" t="n"/>
+      <c r="O16" s="47" t="n"/>
+      <c r="P16" s="62" t="n"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>PRD-02</t>
+        </is>
+      </c>
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Document rules and pitch alignment</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>Dan (A); Nick and Badhri (R); Tamer (C)</t>
+        </is>
+      </c>
+      <c r="D17" s="44" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E17" s="44" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G17" s="47" t="n"/>
+      <c r="H17" s="47" t="n"/>
+      <c r="I17" s="46" t="n"/>
+      <c r="J17" s="46" t="n"/>
+      <c r="K17" s="46" t="n"/>
+      <c r="L17" s="46" t="n"/>
+      <c r="M17" s="46" t="n"/>
+      <c r="N17" s="46" t="n"/>
+      <c r="O17" s="46" t="n"/>
+      <c r="P17" s="63" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>TEC-01</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="inlineStr">
+        <is>
+          <t>Smart contract and contract tests</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>Nick (A/R); Dan (R)</t>
+        </is>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F18" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" s="47" t="n"/>
+      <c r="H18" s="46" t="n"/>
+      <c r="I18" s="46" t="n"/>
+      <c r="J18" s="46" t="n"/>
+      <c r="K18" s="46" t="n"/>
+      <c r="L18" s="47" t="n"/>
+      <c r="M18" s="47" t="n"/>
+      <c r="N18" s="47" t="n"/>
+      <c r="O18" s="47" t="n"/>
+      <c r="P18" s="62" t="n"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="42" t="inlineStr">
+        <is>
+          <t>TEC-02</t>
+        </is>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Application lifecycle, authentication and persistence</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Nick (A/R); Dan (R)</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E19" s="44" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F19" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G19" s="47" t="n"/>
+      <c r="H19" s="47" t="n"/>
+      <c r="I19" s="46" t="n"/>
+      <c r="J19" s="46" t="n"/>
+      <c r="K19" s="46" t="n"/>
+      <c r="L19" s="46" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="46" t="n"/>
+      <c r="P19" s="62" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>TEC-03</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="inlineStr">
+        <is>
+          <t>Testnet deployment and onboarding gate</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>Nick (A); Dan (R)</t>
+        </is>
+      </c>
+      <c r="D20" s="50" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E20" s="50" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F20" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" s="47" t="n"/>
+      <c r="H20" s="47" t="n"/>
+      <c r="I20" s="47" t="n"/>
+      <c r="J20" s="46" t="n"/>
+      <c r="K20" s="46" t="n"/>
+      <c r="L20" s="46" t="n"/>
+      <c r="M20" s="46" t="n"/>
+      <c r="N20" s="46" t="n"/>
+      <c r="O20" s="46" t="n"/>
+      <c r="P20" s="63" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="42" t="inlineStr">
+        <is>
+          <t>TEC-04</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Integrated acceptance and clean-build reproducibility</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>Nick (A/R); Dan (R)</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E21" s="44" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F21" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="n"/>
+      <c r="I21" s="47" t="n"/>
+      <c r="J21" s="47" t="n"/>
+      <c r="K21" s="47" t="n"/>
+      <c r="L21" s="47" t="n"/>
+      <c r="M21" s="47" t="n"/>
+      <c r="N21" s="47" t="n"/>
+      <c r="O21" s="46" t="n"/>
+      <c r="P21" s="63" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>UX-01</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="inlineStr">
+        <is>
+          <t>Role journeys and consolidated dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>Mo (A/R); Nick and Dan (C)</t>
+        </is>
+      </c>
+      <c r="D22" s="50" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E22" s="50" t="n">
+        <v>46242</v>
+      </c>
+      <c r="F22" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G22" s="47" t="n"/>
+      <c r="H22" s="47" t="n"/>
+      <c r="I22" s="46" t="n"/>
+      <c r="J22" s="46" t="n"/>
+      <c r="K22" s="46" t="n"/>
+      <c r="L22" s="46" t="n"/>
+      <c r="M22" s="46" t="n"/>
+      <c r="N22" s="46" t="n"/>
+      <c r="O22" s="46" t="n"/>
+      <c r="P22" s="62" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>UX-02</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>Canonical demo route and polish</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>Mo (A/R); Dan (R); Tamer (C)</t>
+        </is>
+      </c>
+      <c r="D23" s="44" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E23" s="44" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F23" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" s="47" t="n"/>
+      <c r="H23" s="47" t="n"/>
+      <c r="I23" s="47" t="n"/>
+      <c r="J23" s="47" t="n"/>
+      <c r="K23" s="47" t="n"/>
+      <c r="L23" s="47" t="n"/>
+      <c r="M23" s="47" t="n"/>
+      <c r="N23" s="47" t="n"/>
+      <c r="O23" s="46" t="n"/>
+      <c r="P23" s="63" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>UX-03</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="inlineStr">
+        <is>
+          <t>Front-end UI implementation</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>Mo (A/R); Nick and Dan (C); Tamer (I)</t>
+        </is>
+      </c>
+      <c r="D24" s="50" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E24" s="50" t="n">
+        <v>46242</v>
+      </c>
+      <c r="F24" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G24" s="47" t="n"/>
+      <c r="H24" s="47" t="n"/>
+      <c r="I24" s="46" t="n"/>
+      <c r="J24" s="46" t="n"/>
+      <c r="K24" s="46" t="n"/>
+      <c r="L24" s="46" t="n"/>
+      <c r="M24" s="46" t="n"/>
+      <c r="N24" s="46" t="n"/>
+      <c r="O24" s="46" t="n"/>
+      <c r="P24" s="62" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>TEC-05</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Back-end application integration</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>Mo (A/R); Nick and Dan (C); Tamer (I)</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E25" s="44" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F25" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" s="47" t="n"/>
+      <c r="H25" s="47" t="n"/>
+      <c r="I25" s="47" t="n"/>
+      <c r="J25" s="47" t="n"/>
+      <c r="K25" s="47" t="n"/>
+      <c r="L25" s="46" t="n"/>
+      <c r="M25" s="46" t="n"/>
+      <c r="N25" s="46" t="n"/>
+      <c r="O25" s="46" t="n"/>
+      <c r="P25" s="63" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>RISK-01</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>Legal, regulatory and document research</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>Badhri (A/R); Tamer (C)</t>
+        </is>
+      </c>
+      <c r="D26" s="50" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E26" s="50" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F26" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G26" s="46" t="n"/>
+      <c r="H26" s="46" t="n"/>
+      <c r="I26" s="46" t="n"/>
+      <c r="J26" s="46" t="n"/>
+      <c r="K26" s="46" t="n"/>
+      <c r="L26" s="46" t="n"/>
+      <c r="M26" s="46" t="n"/>
+      <c r="N26" s="46" t="n"/>
+      <c r="O26" s="46" t="n"/>
+      <c r="P26" s="62" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>RISK-02</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>Final legal and compliance claim review</t>
+        </is>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>Badhri (A/R); Tamer and Nick (C)</t>
+        </is>
+      </c>
+      <c r="D27" s="44" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E27" s="44" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F27" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" s="47" t="n"/>
+      <c r="H27" s="47" t="n"/>
+      <c r="I27" s="47" t="n"/>
+      <c r="J27" s="47" t="n"/>
+      <c r="K27" s="47" t="n"/>
+      <c r="L27" s="47" t="n"/>
+      <c r="M27" s="47" t="n"/>
+      <c r="N27" s="47" t="n"/>
+      <c r="O27" s="46" t="n"/>
+      <c r="P27" s="63" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>BUS-01</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
+        <is>
+          <t>Financial model, pricing and funding assumptions</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>Conrad (A/R); Mo (R); Tamer (C)</t>
+        </is>
+      </c>
+      <c r="D28" s="50" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E28" s="50" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F28" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" s="46" t="n"/>
+      <c r="H28" s="46" t="n"/>
+      <c r="I28" s="46" t="n"/>
+      <c r="J28" s="46" t="n"/>
+      <c r="K28" s="46" t="n"/>
+      <c r="L28" s="46" t="n"/>
+      <c r="M28" s="46" t="n"/>
+      <c r="N28" s="46" t="n"/>
+      <c r="O28" s="46" t="n"/>
+      <c r="P28" s="63" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="42" t="inlineStr">
+        <is>
+          <t>BUS-02</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>Customer, competitor and market case</t>
+        </is>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>Mo (A/R); Tamer, Conrad and Badhri (C)</t>
+        </is>
+      </c>
+      <c r="D29" s="44" t="n">
+        <v>46182</v>
+      </c>
+      <c r="E29" s="44" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F29" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" s="46" t="n"/>
+      <c r="H29" s="46" t="n"/>
+      <c r="I29" s="46" t="n"/>
+      <c r="J29" s="46" t="n"/>
+      <c r="K29" s="46" t="n"/>
+      <c r="L29" s="46" t="n"/>
+      <c r="M29" s="46" t="n"/>
+      <c r="N29" s="46" t="n"/>
+      <c r="O29" s="46" t="n"/>
+      <c r="P29" s="63" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>BUS-03</t>
+        </is>
+      </c>
+      <c r="B30" s="49" t="inlineStr">
+        <is>
+          <t>Business model and commercial narrative</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="inlineStr">
         <is>
           <t>Tamer (A/R); Conrad and Badhri (C)</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>46234</v>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="22" t="n"/>
-      <c r="P15" s="22" t="n"/>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>PRD-01</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>Product workflow and release rules</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>Dan (A/R); Nick (R)</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>46213</v>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="22" t="n"/>
-      <c r="M16" s="22" t="n"/>
-      <c r="N16" s="22" t="n"/>
-      <c r="O16" s="22" t="n"/>
-      <c r="P16" s="22" t="n"/>
-    </row>
-    <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>PRD-02</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Document rules and pitch alignment</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Dan (A); Nick and Badhri (R); Tamer (C)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="n">
-        <v>46195</v>
-      </c>
-      <c r="E17" s="19" t="n">
+      <c r="D30" s="50" t="n">
         <v>46246</v>
       </c>
-      <c r="F17" s="28" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="n"/>
-      <c r="H17" s="22" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="29" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="29" t="n"/>
-      <c r="N17" s="29" t="n"/>
-      <c r="O17" s="29" t="n"/>
-      <c r="P17" s="29" t="n"/>
-    </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>TEC-01</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>Smart contract and contract tests</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>Nick (A/R); Dan (R)</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>46213</v>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>TEC-02</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Application lifecycle, authentication and persistence</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>Nick (A/R); Dan (R)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>46195</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="22" t="n"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>TEC-03</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Testnet deployment and onboarding gate</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>Nick (A); Dan (R)</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="n">
-        <v>46203</v>
-      </c>
-      <c r="E20" s="25" t="n">
+      <c r="E30" s="50" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F30" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" s="47" t="n"/>
+      <c r="H30" s="47" t="n"/>
+      <c r="I30" s="47" t="n"/>
+      <c r="J30" s="47" t="n"/>
+      <c r="K30" s="47" t="n"/>
+      <c r="L30" s="47" t="n"/>
+      <c r="M30" s="47" t="n"/>
+      <c r="N30" s="47" t="n"/>
+      <c r="O30" s="47" t="n"/>
+      <c r="P30" s="63" t="n"/>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>SUB-01</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Final deck and script</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>Tamer (A/R); Dan and Mo (R); other leads (C)</t>
+        </is>
+      </c>
+      <c r="D31" s="44" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E31" s="44" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F31" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" s="47" t="n"/>
+      <c r="H31" s="47" t="n"/>
+      <c r="I31" s="47" t="n"/>
+      <c r="J31" s="47" t="n"/>
+      <c r="K31" s="47" t="n"/>
+      <c r="L31" s="47" t="n"/>
+      <c r="M31" s="47" t="n"/>
+      <c r="N31" s="46" t="n"/>
+      <c r="O31" s="46" t="n"/>
+      <c r="P31" s="63" t="n"/>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>SUB-02</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="inlineStr">
+        <is>
+          <t>Demo runbook</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>Dan (A/R); Nick (R); Mo (C)</t>
+        </is>
+      </c>
+      <c r="D32" s="50" t="n">
+        <v>46237</v>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>46246</v>
+      </c>
+      <c r="F32" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G32" s="47" t="n"/>
+      <c r="H32" s="47" t="n"/>
+      <c r="I32" s="47" t="n"/>
+      <c r="J32" s="47" t="n"/>
+      <c r="K32" s="47" t="n"/>
+      <c r="L32" s="47" t="n"/>
+      <c r="M32" s="47" t="n"/>
+      <c r="N32" s="47" t="n"/>
+      <c r="O32" s="46" t="n"/>
+      <c r="P32" s="63" t="n"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>SUB-03</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Rehearsals and recordings</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>Dan (A/R); Tamer and Mo (R); Nick (C)</t>
+        </is>
+      </c>
+      <c r="D33" s="44" t="n">
         <v>46244</v>
       </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
-        <is>
-          <t>TEC-04</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>Integrated acceptance and clean-build reproducibility</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>Nick (A/R); Dan (R)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F21" s="28" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G21" s="22" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
-      <c r="K21" s="22" t="n"/>
-      <c r="L21" s="22" t="n"/>
-      <c r="M21" s="22" t="n"/>
-      <c r="N21" s="22" t="n"/>
-      <c r="O21" s="29" t="n"/>
-      <c r="P21" s="29" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>UX-01</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>Role journeys and consolidated dashboard</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>Mo (A/R); Nick and Dan (C)</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="n">
-        <v>46195</v>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>46242</v>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="22" t="n"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>UX-02</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>Canonical demo route and polish</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Mo (A/R); Dan (R); Tamer (C)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F23" s="26" t="inlineStr">
-        <is>
-          <t>Doing</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="22" t="n"/>
-      <c r="J23" s="22" t="n"/>
-      <c r="K23" s="22" t="n"/>
-      <c r="L23" s="22" t="n"/>
-      <c r="M23" s="22" t="n"/>
-      <c r="N23" s="22" t="n"/>
-      <c r="O23" s="27" t="n"/>
-      <c r="P23" s="27" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>RISK-01</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Legal, regulatory and document research</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>Badhri (A/R); Tamer (C)</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E24" s="25" t="n">
-        <v>46239</v>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="22" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>RISK-02</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Final legal and compliance claim review</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>Badhri (A/R); Tamer and Nick (C)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E25" s="19" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F25" s="28" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G25" s="22" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="22" t="n"/>
-      <c r="J25" s="22" t="n"/>
-      <c r="K25" s="22" t="n"/>
-      <c r="L25" s="22" t="n"/>
-      <c r="M25" s="22" t="n"/>
-      <c r="N25" s="22" t="n"/>
-      <c r="O25" s="29" t="n"/>
-      <c r="P25" s="29" t="n"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>BUS-01</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Financial model, pricing and funding assumptions</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Conrad (A/R); Mo (R); Tamer (C)</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E26" s="25" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F26" s="28" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="29" t="n"/>
-      <c r="I26" s="29" t="n"/>
-      <c r="J26" s="29" t="n"/>
-      <c r="K26" s="29" t="n"/>
-      <c r="L26" s="29" t="n"/>
-      <c r="M26" s="29" t="n"/>
-      <c r="N26" s="29" t="n"/>
-      <c r="O26" s="29" t="n"/>
-      <c r="P26" s="29" t="n"/>
-    </row>
-    <row r="27" ht="36" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>BUS-02</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>Customer, competitor and market case</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>Mo (A/R); Tamer, Conrad and Badhri (C)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="n">
-        <v>46182</v>
-      </c>
-      <c r="E27" s="19" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="29" t="n"/>
-      <c r="I27" s="29" t="n"/>
-      <c r="J27" s="29" t="n"/>
-      <c r="K27" s="29" t="n"/>
-      <c r="L27" s="29" t="n"/>
-      <c r="M27" s="29" t="n"/>
-      <c r="N27" s="29" t="n"/>
-      <c r="O27" s="29" t="n"/>
-      <c r="P27" s="29" t="n"/>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>BUS-03</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>Business model and commercial narrative</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>Conrad (A/R); Tamer and Mo (R); Badhri (C)</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="n">
-        <v>46246</v>
-      </c>
-      <c r="E28" s="25" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F28" s="26" t="inlineStr">
-        <is>
-          <t>Doing</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="22" t="n"/>
-      <c r="J28" s="22" t="n"/>
-      <c r="K28" s="22" t="n"/>
-      <c r="L28" s="22" t="n"/>
-      <c r="M28" s="22" t="n"/>
-      <c r="N28" s="22" t="n"/>
-      <c r="O28" s="22" t="n"/>
-      <c r="P28" s="27" t="n"/>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>SUB-01</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Final deck and script</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>Tamer (A/R); Dan and Mo (R); other leads (C)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E29" s="19" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F29" s="26" t="inlineStr">
-        <is>
-          <t>Doing</t>
-        </is>
-      </c>
-      <c r="G29" s="22" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="22" t="n"/>
-      <c r="J29" s="22" t="n"/>
-      <c r="K29" s="22" t="n"/>
-      <c r="L29" s="22" t="n"/>
-      <c r="M29" s="22" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
-    </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>SUB-02</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>Demo runbook</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>Dan (A/R); Nick (R); Mo (C)</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E30" s="25" t="n">
-        <v>46246</v>
-      </c>
-      <c r="F30" s="30" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="n"/>
-      <c r="H30" s="22" t="n"/>
-      <c r="I30" s="22" t="n"/>
-      <c r="J30" s="22" t="n"/>
-      <c r="K30" s="22" t="n"/>
-      <c r="L30" s="22" t="n"/>
-      <c r="M30" s="22" t="n"/>
-      <c r="N30" s="22" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>SUB-03</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>Rehearsals and recordings</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>Dan (A/R); Tamer and Mo (R); Nick (C)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E31" s="19" t="n">
+      <c r="E33" s="44" t="n">
         <v>46247</v>
       </c>
-      <c r="F31" s="30" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G31" s="22" t="n"/>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="22" t="n"/>
-      <c r="J31" s="22" t="n"/>
-      <c r="K31" s="22" t="n"/>
-      <c r="L31" s="22" t="n"/>
-      <c r="M31" s="22" t="n"/>
-      <c r="N31" s="22" t="n"/>
-      <c r="O31" s="22" t="n"/>
-      <c r="P31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="F33" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" s="47" t="n"/>
+      <c r="H33" s="47" t="n"/>
+      <c r="I33" s="47" t="n"/>
+      <c r="J33" s="47" t="n"/>
+      <c r="K33" s="47" t="n"/>
+      <c r="L33" s="47" t="n"/>
+      <c r="M33" s="47" t="n"/>
+      <c r="N33" s="47" t="n"/>
+      <c r="O33" s="47" t="n"/>
+      <c r="P33" s="63" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="48" t="inlineStr">
         <is>
           <t>SUB-04</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>Submission QA and upload</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C34" s="49" t="inlineStr">
         <is>
           <t>Tamer (A/R); Dan (R); Mo (C)</t>
         </is>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D34" s="50" t="n">
         <v>46247</v>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E34" s="50" t="n">
         <v>46248</v>
       </c>
-      <c r="F32" s="30" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="n"/>
-      <c r="H32" s="22" t="n"/>
-      <c r="I32" s="22" t="n"/>
-      <c r="J32" s="22" t="n"/>
-      <c r="K32" s="22" t="n"/>
-      <c r="L32" s="22" t="n"/>
-      <c r="M32" s="22" t="n"/>
-      <c r="N32" s="22" t="n"/>
-      <c r="O32" s="22" t="n"/>
-      <c r="P32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="F34" s="45" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" s="47" t="n"/>
+      <c r="H34" s="47" t="n"/>
+      <c r="I34" s="47" t="n"/>
+      <c r="J34" s="47" t="n"/>
+      <c r="K34" s="47" t="n"/>
+      <c r="L34" s="47" t="n"/>
+      <c r="M34" s="47" t="n"/>
+      <c r="N34" s="47" t="n"/>
+      <c r="O34" s="47" t="n"/>
+      <c r="P34" s="63" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>DEF-01</t>
         </is>
       </c>
-      <c r="B33" s="33" t="inlineStr">
+      <c r="B35" s="56" t="inlineStr">
         <is>
           <t>Post-MVP integrations and production hardening</t>
         </is>
       </c>
-      <c r="C33" s="33" t="inlineStr">
+      <c r="C35" s="56" t="inlineStr">
         <is>
           <t>Tamer (A); technical and domain leads (C)</t>
         </is>
       </c>
-      <c r="D33" s="34" t="n"/>
-      <c r="E33" s="34" t="n"/>
-      <c r="F33" s="35" t="inlineStr">
+      <c r="D35" s="57" t="n"/>
+      <c r="E35" s="57" t="n"/>
+      <c r="F35" s="58" t="inlineStr">
         <is>
           <t>Deferred</t>
         </is>
       </c>
-      <c r="G33" s="36" t="n"/>
-      <c r="H33" s="36" t="n"/>
-      <c r="I33" s="36" t="n"/>
-      <c r="J33" s="36" t="n"/>
-      <c r="K33" s="36" t="n"/>
-      <c r="L33" s="36" t="n"/>
-      <c r="M33" s="36" t="n"/>
-      <c r="N33" s="36" t="n"/>
-      <c r="O33" s="36" t="n"/>
-      <c r="P33" s="36" t="n"/>
+      <c r="G35" s="55" t="n"/>
+      <c r="H35" s="55" t="n"/>
+      <c r="I35" s="55" t="n"/>
+      <c r="J35" s="55" t="n"/>
+      <c r="K35" s="55" t="n"/>
+      <c r="L35" s="55" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="64" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A8:P33"/>
+  <autoFilter ref="A8:P35"/>
   <mergeCells count="18">
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="O7:P7"/>
@@ -1917,42 +2219,42 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G9:P33">
-    <cfRule type="expression" priority="1" dxfId="0">
+  <conditionalFormatting sqref="G9:P35">
+    <cfRule type="expression" priority="11" dxfId="0">
       <formula>AND(G$8&lt;=$E9,G$8+6&gt;=$D9,$F9="Done")</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="13" dxfId="1">
       <formula>AND(G$8&lt;=$E9,G$8+6&gt;=$D9,$F9="Review")</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="15" dxfId="10">
       <formula>AND(G$8&lt;=$E9,G$8+6&gt;=$D9,$F9="Doing")</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="17" dxfId="3">
       <formula>AND(G$8&lt;=$E9,G$8+6&gt;=$D9,$F9="To Do")</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="19" dxfId="11">
       <formula>AND(G$8&lt;=$E9,G$8+6&gt;=$D9,$F9="Deferred")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F33">
-    <cfRule type="expression" priority="6" dxfId="5">
+  <conditionalFormatting sqref="F9:F35">
+    <cfRule type="expression" priority="12" dxfId="5">
       <formula>$F9="Done"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="6">
+    <cfRule type="expression" priority="14" dxfId="6">
       <formula>$F9="Review"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" dxfId="7">
+    <cfRule type="expression" priority="16" dxfId="12">
       <formula>$F9="Doing"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="8">
+    <cfRule type="expression" priority="18" dxfId="8">
       <formula>$F9="To Do"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="9">
+    <cfRule type="expression" priority="20" dxfId="13">
       <formula>$F9="Deferred"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F9:F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid status" error="Choose a controlled v3 status." type="list">
+    <dataValidation sqref="F9:F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Done,Review,Doing,To Do,Deferred"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1966,6 +2268,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing ns1:id="anysvml"/>
 </worksheet>
 </file>